--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2018_T3_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2018_T3_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>88</t>
+    <t>84</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>3.974</t>
-  </si>
-  <si>
-    <t>(0.668)</t>
-  </si>
-  <si>
-    <t>17.909</t>
-  </si>
-  <si>
-    <t>(2.175)</t>
-  </si>
-  <si>
-    <t>85.657</t>
-  </si>
-  <si>
-    <t>(22.372)</t>
-  </si>
-  <si>
-    <t>116.078</t>
-  </si>
-  <si>
-    <t>(34.730)</t>
-  </si>
-  <si>
-    <t>3.359</t>
-  </si>
-  <si>
-    <t>(0.431)</t>
-  </si>
-  <si>
-    <t>18.750</t>
-  </si>
-  <si>
-    <t>(2.170)</t>
-  </si>
-  <si>
-    <t>15.928</t>
-  </si>
-  <si>
-    <t>(7.143)</t>
-  </si>
-  <si>
-    <t>7.160</t>
-  </si>
-  <si>
-    <t>(6.304)</t>
-  </si>
-  <si>
-    <t>119.156</t>
-  </si>
-  <si>
-    <t>(29.319)</t>
-  </si>
-  <si>
-    <t>118.304</t>
-  </si>
-  <si>
-    <t>(42.380)</t>
+    <t>3.822</t>
+  </si>
+  <si>
+    <t>(0.642)</t>
+  </si>
+  <si>
+    <t>18.690</t>
+  </si>
+  <si>
+    <t>(2.243)</t>
+  </si>
+  <si>
+    <t>62.691</t>
+  </si>
+  <si>
+    <t>(12.157)</t>
+  </si>
+  <si>
+    <t>76.820</t>
+  </si>
+  <si>
+    <t>(13.902)</t>
+  </si>
+  <si>
+    <t>3.126</t>
+  </si>
+  <si>
+    <t>(0.350)</t>
+  </si>
+  <si>
+    <t>19.476</t>
+  </si>
+  <si>
+    <t>(2.240)</t>
+  </si>
+  <si>
+    <t>6.320</t>
+  </si>
+  <si>
+    <t>(1.500)</t>
+  </si>
+  <si>
+    <t>0.861</t>
+  </si>
+  <si>
+    <t>(0.116)</t>
+  </si>
+  <si>
+    <t>90.794</t>
+  </si>
+  <si>
+    <t>(16.329)</t>
+  </si>
+  <si>
+    <t>64.590</t>
+  </si>
+  <si>
+    <t>(11.811)</t>
   </si>
   <si>
     <t>26</t>
@@ -198,7 +198,7 @@
     <t>(33.890)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>-0.989</t>
-  </si>
-  <si>
-    <t>0.476</t>
-  </si>
-  <si>
-    <t>57.451</t>
-  </si>
-  <si>
-    <t>37.733</t>
-  </si>
-  <si>
-    <t>-0.896</t>
-  </si>
-  <si>
-    <t>0.288</t>
-  </si>
-  <si>
-    <t>-11.419</t>
-  </si>
-  <si>
-    <t>-6.414</t>
-  </si>
-  <si>
-    <t>52.977</t>
-  </si>
-  <si>
-    <t>19.103</t>
+    <t>-0.837</t>
+  </si>
+  <si>
+    <t>-0.306</t>
+  </si>
+  <si>
+    <t>80.417***</t>
+  </si>
+  <si>
+    <t>76.991**</t>
+  </si>
+  <si>
+    <t>-0.662</t>
+  </si>
+  <si>
+    <t>-0.438</t>
+  </si>
+  <si>
+    <t>-1.811</t>
+  </si>
+  <si>
+    <t>-0.115</t>
+  </si>
+  <si>
+    <t>81.339**</t>
+  </si>
+  <si>
+    <t>72.817**</t>
   </si>
 </sst>
 </file>
